--- a/Data/uncertainty/pv.xlsx
+++ b/Data/uncertainty/pv.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="12255"/>
+    <workbookView windowWidth="20752" windowHeight="9555"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -77,13 +77,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -551,148 +544,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1048,15 +1041,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N97"/>
+  <dimension ref="A1:R97"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="15.2035398230088" customWidth="1"/>
     <col min="3" max="3" width="13.6814159292035" customWidth="1"/>
     <col min="4" max="4" width="16.7345132743363" customWidth="1"/>
+    <col min="9" max="9" width="12.7964601769912"/>
+    <col min="13" max="13" width="13.858407079646"/>
+    <col min="15" max="15" width="12.7964601769912"/>
+    <col min="17" max="17" width="12.7964601769912"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14">
+    <row r="1" spans="2:18">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1067,27 +1064,31 @@
         <v>2</v>
       </c>
       <c r="G1" s="2"/>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="2"/>
+      <c r="I1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2"/>
+      <c r="M1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="N1" s="2"/>
+      <c r="O1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="2"/>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="R1" s="2"/>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1108,30 +1109,46 @@
         <v>1.60728738915751</v>
       </c>
       <c r="I2" s="2">
+        <f ca="1">H2*2</f>
+        <v>3.21457477831502</v>
+      </c>
+      <c r="J2" s="2">
         <v>0.969885</v>
       </c>
-      <c r="J2" s="2">
-        <f ca="1" t="shared" ref="J2:J25" si="0">H2*I2</f>
+      <c r="K2" s="2">
+        <f ca="1" t="shared" ref="K2:K25" si="0">H2*J2</f>
         <v>1.55888392943303</v>
       </c>
-      <c r="K2" s="2">
+      <c r="L2" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C1)-1)*4,0)</f>
         <v>1.55608226196628</v>
       </c>
-      <c r="L2" s="2">
+      <c r="M2" s="2">
+        <f ca="1">L2*2</f>
+        <v>3.11216452393256</v>
+      </c>
+      <c r="N2" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D1)-1)*4,0)</f>
         <v>1.65849251634873</v>
       </c>
-      <c r="M2" s="2">
-        <f ca="1" t="shared" ref="M2:M25" si="1">IF(OR(J2&gt;K2,J2&lt;L2),J2,H2)</f>
+      <c r="O2" s="2">
+        <f ca="1">N2*2</f>
+        <v>3.31698503269746</v>
+      </c>
+      <c r="P2" s="2">
+        <f ca="1" t="shared" ref="P2:P25" si="1">IF(OR(K2&gt;L2,K2&lt;N2),K2,H2)</f>
         <v>1.55888392943303</v>
       </c>
-      <c r="N2" s="2">
-        <f ca="1" t="shared" ref="N2:N25" si="2">IF(H2=M2,0,1)</f>
+      <c r="Q2" s="2">
+        <f ca="1">P2*2</f>
+        <v>3.11776785886606</v>
+      </c>
+      <c r="R2" s="2">
+        <f ca="1" t="shared" ref="R2:R25" si="2">IF(H2=P2,0,1)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:18">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1152,30 +1169,46 @@
         <v>1.43437286015242</v>
       </c>
       <c r="I3" s="2">
+        <f ca="1" t="shared" ref="I3:I25" si="3">H3*2</f>
+        <v>2.86874572030484</v>
+      </c>
+      <c r="J3" s="2">
         <v>1.021257</v>
       </c>
-      <c r="J3" s="2">
+      <c r="K3" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>1.46486332404068</v>
       </c>
-      <c r="K3" s="2">
+      <c r="L3" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C2)-1)*4,0)</f>
         <v>1.383912474186</v>
       </c>
-      <c r="L3" s="2">
+      <c r="M3" s="2">
+        <f ca="1" t="shared" ref="M3:M25" si="4">L3*2</f>
+        <v>2.767824948372</v>
+      </c>
+      <c r="N3" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D2)-1)*4,0)</f>
         <v>1.48483324611884</v>
       </c>
-      <c r="M3" s="2">
+      <c r="O3" s="2">
+        <f ca="1" t="shared" ref="O3:O25" si="5">N3*2</f>
+        <v>2.96966649223768</v>
+      </c>
+      <c r="P3" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>1.46486332404068</v>
       </c>
-      <c r="N3" s="2">
+      <c r="Q3" s="2">
+        <f ca="1" t="shared" ref="Q3:Q25" si="6">P3*2</f>
+        <v>2.92972664808136</v>
+      </c>
+      <c r="R3" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:18">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1196,30 +1229,46 @@
         <v>1.63669116340175</v>
       </c>
       <c r="I4" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>3.2733823268035</v>
+      </c>
+      <c r="J4" s="2">
         <v>0.997038</v>
       </c>
-      <c r="J4" s="2">
+      <c r="K4" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>1.63184328417575</v>
       </c>
-      <c r="K4" s="2">
+      <c r="L4" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C3)-1)*4,0)</f>
         <v>1.55547802335185</v>
       </c>
-      <c r="L4" s="2">
+      <c r="M4" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>3.1109560467037</v>
+      </c>
+      <c r="N4" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D3)-1)*4,0)</f>
         <v>1.71790430345165</v>
       </c>
-      <c r="M4" s="2">
+      <c r="O4" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>3.4358086069033</v>
+      </c>
+      <c r="P4" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>1.63184328417575</v>
       </c>
-      <c r="N4" s="2">
+      <c r="Q4" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>3.26368656835151</v>
+      </c>
+      <c r="R4" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:18">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1240,30 +1289,46 @@
         <v>1.94309103664992</v>
       </c>
       <c r="I5" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>3.88618207329984</v>
+      </c>
+      <c r="J5" s="2">
         <v>1.03662</v>
       </c>
-      <c r="J5" s="2">
+      <c r="K5" s="2">
         <f ca="1" t="shared" si="0"/>
-        <v>2.01424703041205</v>
-      </c>
-      <c r="K5" s="2">
+        <v>2.01424703041204</v>
+      </c>
+      <c r="L5" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C4)-1)*4,0)</f>
         <v>1.88635244027236</v>
       </c>
-      <c r="L5" s="2">
+      <c r="M5" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>3.77270488054472</v>
+      </c>
+      <c r="N5" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D4)-1)*4,0)</f>
         <v>1.99982963302749</v>
       </c>
-      <c r="M5" s="2">
+      <c r="O5" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>3.99965926605498</v>
+      </c>
+      <c r="P5" s="2">
         <f ca="1" t="shared" si="1"/>
-        <v>2.01424703041205</v>
-      </c>
-      <c r="N5" s="2">
+        <v>2.01424703041204</v>
+      </c>
+      <c r="Q5" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>4.02849406082408</v>
+      </c>
+      <c r="R5" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:18">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1284,30 +1349,46 @@
         <v>1.64904316643282</v>
       </c>
       <c r="I6" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>3.29808633286564</v>
+      </c>
+      <c r="J6" s="2">
         <v>1.034074</v>
       </c>
-      <c r="J6" s="2">
+      <c r="K6" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>1.70523266328585</v>
       </c>
-      <c r="K6" s="2">
+      <c r="L6" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C5)-1)*4,0)</f>
         <v>1.60361276744509</v>
       </c>
-      <c r="L6" s="2">
+      <c r="M6" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>3.20722553489018</v>
+      </c>
+      <c r="N6" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D5)-1)*4,0)</f>
         <v>1.69447356542056</v>
       </c>
-      <c r="M6" s="2">
+      <c r="O6" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>3.38894713084112</v>
+      </c>
+      <c r="P6" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>1.70523266328585</v>
       </c>
-      <c r="N6" s="2">
+      <c r="Q6" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>3.4104653265717</v>
+      </c>
+      <c r="R6" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:18">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1328,30 +1409,46 @@
         <v>1.2460589072752</v>
       </c>
       <c r="I7" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>2.4921178145504</v>
+      </c>
+      <c r="J7" s="2">
         <v>0.988478</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>1.23170181654558</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C6)-1)*4,0)</f>
         <v>1.16625645981652</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>2.33251291963304</v>
+      </c>
+      <c r="N7" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D6)-1)*4,0)</f>
         <v>1.32586135473389</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>2.65172270946778</v>
+      </c>
+      <c r="P7" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>1.23170181654558</v>
       </c>
-      <c r="N7" s="2">
+      <c r="Q7" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>2.46340363309115</v>
+      </c>
+      <c r="R7" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:18">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1372,30 +1469,46 @@
         <v>0.433202665878096</v>
       </c>
       <c r="I8" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>0.866405331756192</v>
+      </c>
+      <c r="J8" s="2">
         <v>1.00025</v>
       </c>
-      <c r="J8" s="2">
+      <c r="K8" s="2">
         <f ca="1" t="shared" si="0"/>
-        <v>0.433310966544565</v>
-      </c>
-      <c r="K8" s="2">
+        <v>0.433310966544566</v>
+      </c>
+      <c r="L8" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C7)-1)*4,0)</f>
         <v>0.379615890712904</v>
       </c>
-      <c r="L8" s="2">
+      <c r="M8" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>0.759231781425808</v>
+      </c>
+      <c r="N8" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D7)-1)*4,0)</f>
         <v>0.486789441043288</v>
       </c>
-      <c r="M8" s="2">
+      <c r="O8" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>0.973578882086576</v>
+      </c>
+      <c r="P8" s="2">
         <f ca="1" t="shared" si="1"/>
-        <v>0.433310966544565</v>
-      </c>
-      <c r="N8" s="2">
+        <v>0.433310966544566</v>
+      </c>
+      <c r="Q8" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>0.866621933089131</v>
+      </c>
+      <c r="R8" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:18">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1416,30 +1529,46 @@
         <v>0.660079018176577</v>
       </c>
       <c r="I9" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>1.32015803635315</v>
+      </c>
+      <c r="J9" s="2">
         <v>1.037387</v>
       </c>
-      <c r="J9" s="2">
+      <c r="K9" s="2">
         <f ca="1" t="shared" si="0"/>
-        <v>0.684757392429144</v>
-      </c>
-      <c r="K9" s="2">
+        <v>0.684757392429145</v>
+      </c>
+      <c r="L9" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C8)-1)*4,0)</f>
         <v>0.613190589907034</v>
       </c>
-      <c r="L9" s="2">
+      <c r="M9" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>1.22638117981407</v>
+      </c>
+      <c r="N9" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D8)-1)*4,0)</f>
         <v>0.70696744644612</v>
       </c>
-      <c r="M9" s="2">
+      <c r="O9" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>1.41393489289224</v>
+      </c>
+      <c r="P9" s="2">
         <f ca="1" t="shared" si="1"/>
-        <v>0.684757392429144</v>
-      </c>
-      <c r="N9" s="2">
+        <v>0.684757392429145</v>
+      </c>
+      <c r="Q9" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>1.36951478485829</v>
+      </c>
+      <c r="R9" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:18">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1460,30 +1589,46 @@
         <v>38.465</v>
       </c>
       <c r="I10" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>76.93</v>
+      </c>
+      <c r="J10" s="2">
         <v>1.045036</v>
       </c>
-      <c r="J10" s="2">
+      <c r="K10" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>40.19730974</v>
       </c>
-      <c r="K10" s="2">
+      <c r="L10" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C9)-1)*4,0)</f>
         <v>35.1417291689057</v>
       </c>
-      <c r="L10" s="2">
+      <c r="M10" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>70.2834583378114</v>
+      </c>
+      <c r="N10" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D9)-1)*4,0)</f>
         <v>41.7882708310943</v>
       </c>
-      <c r="M10" s="2">
+      <c r="O10" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>83.5765416621886</v>
+      </c>
+      <c r="P10" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>40.19730974</v>
       </c>
-      <c r="N10" s="2">
+      <c r="Q10" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>80.39461948</v>
+      </c>
+      <c r="R10" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:18">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1504,30 +1649,46 @@
         <v>109.3575</v>
       </c>
       <c r="I11" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>218.715</v>
+      </c>
+      <c r="J11" s="2">
         <v>0.986436</v>
       </c>
-      <c r="J11" s="2">
+      <c r="K11" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>107.87417487</v>
       </c>
-      <c r="K11" s="2">
+      <c r="L11" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C10)-1)*4,0)</f>
         <v>97.9735594391906</v>
       </c>
-      <c r="L11" s="2">
+      <c r="M11" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>195.947118878381</v>
+      </c>
+      <c r="N11" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D10)-1)*4,0)</f>
         <v>120.741440560809</v>
       </c>
-      <c r="M11" s="2">
+      <c r="O11" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>241.482881121618</v>
+      </c>
+      <c r="P11" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>107.87417487</v>
       </c>
-      <c r="N11" s="2">
+      <c r="Q11" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>215.74834974</v>
+      </c>
+      <c r="R11" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:18">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1548,30 +1709,46 @@
         <v>226.39</v>
       </c>
       <c r="I12" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>452.78</v>
+      </c>
+      <c r="J12" s="2">
         <v>0.972533</v>
       </c>
-      <c r="J12" s="2">
+      <c r="K12" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>220.17174587</v>
       </c>
-      <c r="K12" s="2">
+      <c r="L12" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C11)-1)*4,0)</f>
         <v>189.493032151142</v>
       </c>
-      <c r="L12" s="2">
+      <c r="M12" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>378.986064302284</v>
+      </c>
+      <c r="N12" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D11)-1)*4,0)</f>
         <v>263.286967848858</v>
       </c>
-      <c r="M12" s="2">
+      <c r="O12" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>526.573935697716</v>
+      </c>
+      <c r="P12" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>220.17174587</v>
       </c>
-      <c r="N12" s="2">
+      <c r="Q12" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>440.34349174</v>
+      </c>
+      <c r="R12" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:18">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1592,30 +1769,46 @@
         <v>280.2725</v>
       </c>
       <c r="I13" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>560.545</v>
+      </c>
+      <c r="J13" s="2">
         <v>1.006938</v>
       </c>
-      <c r="J13" s="2">
+      <c r="K13" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>282.217030605</v>
       </c>
-      <c r="K13" s="2">
+      <c r="L13" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C12)-1)*4,0)</f>
         <v>219.640700030149</v>
       </c>
-      <c r="L13" s="2">
+      <c r="M13" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>439.281400060298</v>
+      </c>
+      <c r="N13" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D12)-1)*4,0)</f>
         <v>340.904299969851</v>
       </c>
-      <c r="M13" s="2">
+      <c r="O13" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>681.808599939702</v>
+      </c>
+      <c r="P13" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>282.217030605</v>
       </c>
-      <c r="N13" s="2">
+      <c r="Q13" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>564.43406121</v>
+      </c>
+      <c r="R13" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:18">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1636,30 +1829,46 @@
         <v>273.73</v>
       </c>
       <c r="I14" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>547.46</v>
+      </c>
+      <c r="J14" s="2">
         <v>1.024603</v>
       </c>
-      <c r="J14" s="2">
+      <c r="K14" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>280.46457919</v>
       </c>
-      <c r="K14" s="2">
+      <c r="L14" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C13)-1)*4,0)</f>
         <v>208.399000329279</v>
       </c>
-      <c r="L14" s="2">
+      <c r="M14" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>416.798000658558</v>
+      </c>
+      <c r="N14" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D13)-1)*4,0)</f>
         <v>339.060999670721</v>
       </c>
-      <c r="M14" s="2">
+      <c r="O14" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>678.121999341442</v>
+      </c>
+      <c r="P14" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>280.46457919</v>
       </c>
-      <c r="N14" s="2">
+      <c r="Q14" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>560.92915838</v>
+      </c>
+      <c r="R14" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:18">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1680,30 +1889,46 @@
         <v>243.505</v>
       </c>
       <c r="I15" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>487.01</v>
+      </c>
+      <c r="J15" s="2">
         <v>0.985</v>
       </c>
-      <c r="J15" s="2">
+      <c r="K15" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>239.852425</v>
       </c>
-      <c r="K15" s="2">
+      <c r="L15" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C14)-1)*4,0)</f>
         <v>212.882270711686</v>
       </c>
-      <c r="L15" s="2">
+      <c r="M15" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>425.764541423372</v>
+      </c>
+      <c r="N15" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D14)-1)*4,0)</f>
         <v>274.127729288314</v>
       </c>
-      <c r="M15" s="2">
+      <c r="O15" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>548.255458576628</v>
+      </c>
+      <c r="P15" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>239.852425</v>
       </c>
-      <c r="N15" s="2">
+      <c r="Q15" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>479.70485</v>
+      </c>
+      <c r="R15" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:18">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1724,30 +1949,46 @@
         <v>211.8275</v>
       </c>
       <c r="I16" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>423.655</v>
+      </c>
+      <c r="J16" s="2">
         <v>0.989829</v>
       </c>
-      <c r="J16" s="2">
+      <c r="K16" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>209.6730024975</v>
       </c>
-      <c r="K16" s="2">
+      <c r="L16" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C15)-1)*4,0)</f>
         <v>167.219913792104</v>
       </c>
-      <c r="L16" s="2">
+      <c r="M16" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>334.439827584208</v>
+      </c>
+      <c r="N16" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D15)-1)*4,0)</f>
         <v>256.435086207896</v>
       </c>
-      <c r="M16" s="2">
+      <c r="O16" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>512.870172415792</v>
+      </c>
+      <c r="P16" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>209.6730024975</v>
       </c>
-      <c r="N16" s="2">
+      <c r="Q16" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>419.346004995</v>
+      </c>
+      <c r="R16" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:18">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1768,30 +2009,46 @@
         <v>137.8575</v>
       </c>
       <c r="I17" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>275.715</v>
+      </c>
+      <c r="J17" s="2">
         <v>0.997796</v>
       </c>
-      <c r="J17" s="2">
+      <c r="K17" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>137.55366207</v>
       </c>
-      <c r="K17" s="2">
+      <c r="L17" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C16)-1)*4,0)</f>
         <v>121.425214361155</v>
       </c>
-      <c r="L17" s="2">
+      <c r="M17" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>242.85042872231</v>
+      </c>
+      <c r="N17" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D16)-1)*4,0)</f>
         <v>154.289785638845</v>
       </c>
-      <c r="M17" s="2">
+      <c r="O17" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>308.57957127769</v>
+      </c>
+      <c r="P17" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>137.55366207</v>
       </c>
-      <c r="N17" s="2">
+      <c r="Q17" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>275.10732414</v>
+      </c>
+      <c r="R17" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:18">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1812,30 +2069,46 @@
         <v>57.2</v>
       </c>
       <c r="I18" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>114.4</v>
+      </c>
+      <c r="J18" s="2">
         <v>0.964075</v>
       </c>
-      <c r="J18" s="2">
+      <c r="K18" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>55.14509</v>
       </c>
-      <c r="K18" s="2">
+      <c r="L18" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C17)-1)*4,0)</f>
         <v>44.1081675280479</v>
       </c>
-      <c r="L18" s="2">
+      <c r="M18" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>88.2163350560958</v>
+      </c>
+      <c r="N18" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D17)-1)*4,0)</f>
         <v>70.2918324719521</v>
       </c>
-      <c r="M18" s="2">
+      <c r="O18" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>140.583664943904</v>
+      </c>
+      <c r="P18" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>55.14509</v>
       </c>
-      <c r="N18" s="2">
+      <c r="Q18" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>110.29018</v>
+      </c>
+      <c r="R18" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:18">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1856,30 +2129,46 @@
         <v>4.295</v>
       </c>
       <c r="I19" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>8.59</v>
+      </c>
+      <c r="J19" s="2">
         <v>0.964811</v>
       </c>
-      <c r="J19" s="2">
+      <c r="K19" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>4.143863245</v>
       </c>
-      <c r="K19" s="2">
+      <c r="L19" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C18)-1)*4,0)</f>
         <v>-0.0519094295368312</v>
       </c>
-      <c r="L19" s="2">
+      <c r="M19" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>-0.103818859073662</v>
+      </c>
+      <c r="N19" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D18)-1)*4,0)</f>
         <v>8.64190942953683</v>
       </c>
-      <c r="M19" s="2">
+      <c r="O19" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>17.2838188590737</v>
+      </c>
+      <c r="P19" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>4.143863245</v>
       </c>
-      <c r="N19" s="2">
+      <c r="Q19" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>8.28772649</v>
+      </c>
+      <c r="R19" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:18">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1900,30 +2189,46 @@
         <v>1.67635289761096</v>
       </c>
       <c r="I20" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>3.35270579522192</v>
+      </c>
+      <c r="J20" s="2">
         <v>1.033227</v>
       </c>
-      <c r="J20" s="2">
+      <c r="K20" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>1.73205307533988</v>
       </c>
-      <c r="K20" s="2">
+      <c r="L20" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C19)-1)*4,0)</f>
         <v>1.14380272436823</v>
       </c>
-      <c r="L20" s="2">
+      <c r="M20" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>2.28760544873646</v>
+      </c>
+      <c r="N20" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D19)-1)*4,0)</f>
         <v>2.20890307085369</v>
       </c>
-      <c r="M20" s="2">
+      <c r="O20" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>4.41780614170738</v>
+      </c>
+      <c r="P20" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>1.73205307533988</v>
       </c>
-      <c r="N20" s="2">
+      <c r="Q20" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>3.46410615067976</v>
+      </c>
+      <c r="R20" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:18">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1944,30 +2249,46 @@
         <v>1.32961672752064</v>
       </c>
       <c r="I21" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>2.65923345504128</v>
+      </c>
+      <c r="J21" s="2">
         <v>1.031367</v>
       </c>
-      <c r="J21" s="2">
+      <c r="K21" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>1.37132281541278</v>
       </c>
-      <c r="K21" s="2">
+      <c r="L21" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C20)-1)*4,0)</f>
         <v>1.24951614879473</v>
       </c>
-      <c r="L21" s="2">
+      <c r="M21" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>2.49903229758946</v>
+      </c>
+      <c r="N21" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D20)-1)*4,0)</f>
         <v>1.40971730624656</v>
       </c>
-      <c r="M21" s="2">
+      <c r="O21" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>2.81943461249312</v>
+      </c>
+      <c r="P21" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>1.37132281541278</v>
       </c>
-      <c r="N21" s="2">
+      <c r="Q21" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>2.74264563082556</v>
+      </c>
+      <c r="R21" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:18">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1988,30 +2309,46 @@
         <v>2.00155275633046</v>
       </c>
       <c r="I22" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>4.00310551266092</v>
+      </c>
+      <c r="J22" s="2">
         <v>0.963888</v>
       </c>
-      <c r="J22" s="2">
+      <c r="K22" s="2">
         <f ca="1" t="shared" si="0"/>
-        <v>1.92927268319386</v>
-      </c>
-      <c r="K22" s="2">
+        <v>1.92927268319385</v>
+      </c>
+      <c r="L22" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C21)-1)*4,0)</f>
         <v>1.9586624089722</v>
       </c>
-      <c r="L22" s="2">
+      <c r="M22" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>3.9173248179444</v>
+      </c>
+      <c r="N22" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D21)-1)*4,0)</f>
         <v>2.04444310368872</v>
       </c>
-      <c r="M22" s="2">
+      <c r="O22" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>4.08888620737744</v>
+      </c>
+      <c r="P22" s="2">
         <f ca="1" t="shared" si="1"/>
-        <v>1.92927268319386</v>
-      </c>
-      <c r="N22" s="2">
+        <v>1.92927268319385</v>
+      </c>
+      <c r="Q22" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>3.85854536638771</v>
+      </c>
+      <c r="R22" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:18">
       <c r="A23">
         <v>21</v>
       </c>
@@ -2032,30 +2369,46 @@
         <v>1.5803153218469</v>
       </c>
       <c r="I23" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>3.1606306436938</v>
+      </c>
+      <c r="J23" s="2">
         <v>0.956548</v>
       </c>
-      <c r="J23" s="2">
+      <c r="K23" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>1.51164746048201</v>
       </c>
-      <c r="K23" s="2">
+      <c r="L23" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C22)-1)*4,0)</f>
         <v>1.50574448773613</v>
       </c>
-      <c r="L23" s="2">
+      <c r="M23" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>3.01148897547226</v>
+      </c>
+      <c r="N23" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D22)-1)*4,0)</f>
         <v>1.65488615595767</v>
       </c>
-      <c r="M23" s="2">
+      <c r="O23" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>3.30977231191534</v>
+      </c>
+      <c r="P23" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>1.51164746048201</v>
       </c>
-      <c r="N23" s="2">
+      <c r="Q23" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>3.02329492096402</v>
+      </c>
+      <c r="R23" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:18">
       <c r="A24">
         <v>22</v>
       </c>
@@ -2076,30 +2429,46 @@
         <v>1.53572837327924</v>
       </c>
       <c r="I24" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>3.07145674655848</v>
+      </c>
+      <c r="J24" s="2">
         <v>0.971773</v>
       </c>
-      <c r="J24" s="2">
+      <c r="K24" s="2">
         <f ca="1" t="shared" si="0"/>
         <v>1.49237936848669</v>
       </c>
-      <c r="K24" s="2">
+      <c r="L24" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C23)-1)*4,0)</f>
         <v>1.47911347139451</v>
       </c>
-      <c r="L24" s="2">
+      <c r="M24" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>2.95822694278902</v>
+      </c>
+      <c r="N24" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D23)-1)*4,0)</f>
         <v>1.59234327516397</v>
       </c>
-      <c r="M24" s="2">
+      <c r="O24" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>3.18468655032794</v>
+      </c>
+      <c r="P24" s="2">
         <f ca="1" t="shared" si="1"/>
         <v>1.49237936848669</v>
       </c>
-      <c r="N24" s="2">
+      <c r="Q24" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>2.98475873697337</v>
+      </c>
+      <c r="R24" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:18">
       <c r="A25">
         <v>23</v>
       </c>
@@ -2120,25 +2489,41 @@
         <v>1.65696851884332</v>
       </c>
       <c r="I25" s="2">
+        <f ca="1" t="shared" si="3"/>
+        <v>3.31393703768664</v>
+      </c>
+      <c r="J25" s="2">
         <v>0.975908</v>
       </c>
-      <c r="J25" s="2">
+      <c r="K25" s="2">
         <f ca="1" t="shared" si="0"/>
-        <v>1.61704883328734</v>
-      </c>
-      <c r="K25" s="2">
+        <v>1.61704883328735</v>
+      </c>
+      <c r="L25" s="2">
         <f ca="1">OFFSET($C$2,(ROW(C24)-1)*4,0)</f>
         <v>1.60102629314012</v>
       </c>
-      <c r="L25" s="2">
+      <c r="M25" s="2">
+        <f ca="1" t="shared" si="4"/>
+        <v>3.20205258628024</v>
+      </c>
+      <c r="N25" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D24)-1)*4,0)</f>
         <v>1.71291074454652</v>
       </c>
-      <c r="M25" s="2">
+      <c r="O25" s="2">
+        <f ca="1" t="shared" si="5"/>
+        <v>3.42582148909304</v>
+      </c>
+      <c r="P25" s="2">
         <f ca="1" t="shared" si="1"/>
-        <v>1.61704883328734</v>
-      </c>
-      <c r="N25" s="2">
+        <v>1.61704883328735</v>
+      </c>
+      <c r="Q25" s="2">
+        <f ca="1" t="shared" si="6"/>
+        <v>3.23409766657469</v>
+      </c>
+      <c r="R25" s="2">
         <f ca="1" t="shared" si="2"/>
         <v>1</v>
       </c>

--- a/Data/uncertainty/pv.xlsx
+++ b/Data/uncertainty/pv.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20752" windowHeight="9555"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1044,13 +1044,13 @@
   <dimension ref="A1:R97"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="15.2035398230088" customWidth="1"/>
-    <col min="3" max="3" width="13.6814159292035" customWidth="1"/>
-    <col min="4" max="4" width="16.7345132743363" customWidth="1"/>
-    <col min="9" max="9" width="12.7964601769912"/>
-    <col min="13" max="13" width="13.858407079646"/>
-    <col min="15" max="15" width="12.7964601769912"/>
-    <col min="17" max="17" width="12.7964601769912"/>
+    <col min="2" max="2" width="15.2" customWidth="1"/>
+    <col min="3" max="3" width="13.6833333333333" customWidth="1"/>
+    <col min="4" max="4" width="16.7333333333333" customWidth="1"/>
+    <col min="9" max="9" width="12.8"/>
+    <col min="13" max="13" width="13.8583333333333"/>
+    <col min="15" max="15" width="12.8"/>
+    <col min="17" max="17" width="12.8"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:18">
@@ -2140,12 +2140,10 @@
         <v>4.143863245</v>
       </c>
       <c r="L19" s="2">
-        <f ca="1">OFFSET($C$2,(ROW(C18)-1)*4,0)</f>
-        <v>-0.0519094295368312</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2">
-        <f ca="1" t="shared" si="4"/>
-        <v>-0.103818859073662</v>
+        <v>0</v>
       </c>
       <c r="N19" s="2">
         <f ca="1">OFFSET($D$2,(ROW(D18)-1)*4,0)</f>
